--- a/JJsonde_reminder.xlsx
+++ b/JJsonde_reminder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BS_LeDuyBinh\automation\zaloAuto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFBB352-30E9-4D9C-8161-079084DB30E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E58E24-03EE-4D14-9136-D548C4E42254}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="52">
   <si>
     <t>PatientID</t>
   </si>
@@ -34,21 +34,6 @@
     <t>OperationDate</t>
   </si>
   <si>
-    <t>22/02/2026</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn A</t>
-  </si>
-  <si>
-    <t>Trần Thị B</t>
-  </si>
-  <si>
-    <t>22/10/2025</t>
-  </si>
-  <si>
-    <t>RemovalTime</t>
-  </si>
-  <si>
     <t>Gender</t>
   </si>
   <si>
@@ -58,12 +43,6 @@
     <t>Female</t>
   </si>
   <si>
-    <t>0965231930</t>
-  </si>
-  <si>
-    <t>0356106272</t>
-  </si>
-  <si>
     <t>Dx</t>
   </si>
   <si>
@@ -73,20 +52,137 @@
     <t>TLT</t>
   </si>
   <si>
-    <t>Lê Văn C</t>
-  </si>
-  <si>
-    <t>PhoneNumber</t>
-  </si>
-  <si>
-    <t>03573119111</t>
+    <t>Đỗ Mạnh Trưởng</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Tài</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Thức</t>
+  </si>
+  <si>
+    <t>Phương Thị Sen</t>
+  </si>
+  <si>
+    <t>Lê Văn Sửu</t>
+  </si>
+  <si>
+    <t>Phạm Văn Bắc</t>
+  </si>
+  <si>
+    <t>Joshua Benjamin Barrass</t>
+  </si>
+  <si>
+    <t>Trần Minh Quang</t>
+  </si>
+  <si>
+    <t>Doãn Thị Hải Yến</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoài Giang</t>
+  </si>
+  <si>
+    <t>Đặng Việt Hùng</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Việt</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Ngọc</t>
+  </si>
+  <si>
+    <t>Chử Đại Hải</t>
+  </si>
+  <si>
+    <t>0912 442 775</t>
+  </si>
+  <si>
+    <t>0943 227 890</t>
+  </si>
+  <si>
+    <t>0905 061 978</t>
+  </si>
+  <si>
+    <t>0912 175 971</t>
+  </si>
+  <si>
+    <t>0837893181</t>
+  </si>
+  <si>
+    <t>0906150357</t>
+  </si>
+  <si>
+    <t>0972097519</t>
+  </si>
+  <si>
+    <t>0988667651</t>
+  </si>
+  <si>
+    <t>0342086382</t>
+  </si>
+  <si>
+    <t>0968419933</t>
+  </si>
+  <si>
+    <t>0978485131</t>
+  </si>
+  <si>
+    <t>0398467174</t>
+  </si>
+  <si>
+    <t>0902249935</t>
+  </si>
+  <si>
+    <t>037394864</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>PhoneNumber_1</t>
+  </si>
+  <si>
+    <t>PhoneNumber_2</t>
+  </si>
+  <si>
+    <t>0985930016</t>
+  </si>
+  <si>
+    <t>0965225672</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>DischargeDate</t>
+  </si>
+  <si>
+    <t>TimeToReVisit</t>
+  </si>
+  <si>
+    <t>FirstReminderDate</t>
+  </si>
+  <si>
+    <t>SecondReminderDate</t>
+  </si>
+  <si>
+    <t>ThirdReminderDate</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>Age</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -221,6 +317,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -403,7 +505,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -518,6 +620,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -563,9 +680,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -887,18 +1010,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.09765625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="15.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.8984375" customWidth="1"/>
+    <col min="10" max="10" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.69921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.09765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -909,101 +1039,527 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>2511041725</v>
+      </c>
+      <c r="B2" s="2">
+        <v>2511041725</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J2">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>2511180543</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2511180543</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3">
+        <v>90</v>
+      </c>
+      <c r="K3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>2512140035</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2512140035</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4">
+        <v>7</v>
+      </c>
+      <c r="K4" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="5" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>2512170189</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2512170189</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5">
+        <v>14</v>
+      </c>
+      <c r="K5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>2512251368</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2512251368</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6">
+        <v>90</v>
+      </c>
+      <c r="K6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>2601091619</v>
+      </c>
+      <c r="B7" s="2">
+        <v>2601091619</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7">
+        <v>7</v>
+      </c>
+      <c r="K7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>2601151746</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2601151746</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8">
+        <v>14</v>
+      </c>
+      <c r="K8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>2601191279</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2601191279</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9">
+        <v>90</v>
+      </c>
+      <c r="K9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>2601231940</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2601231940</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10">
+        <v>7</v>
+      </c>
+      <c r="K10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>2602123397</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2602123397</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11">
+        <v>14</v>
+      </c>
+      <c r="K11" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="12" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>2602261042</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2602261042</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12">
+        <v>90</v>
+      </c>
+      <c r="K12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>2602260176</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2602260176</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13">
+        <v>7</v>
+      </c>
+      <c r="K13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>2603090988</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2603090988</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14">
         <v>14</v>
       </c>
+      <c r="K14" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>20251111</v>
-      </c>
-      <c r="B2">
-        <v>20252222</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="15" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>2603090460</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2603090460</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2">
+      <c r="F15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15">
+        <v>90</v>
+      </c>
+      <c r="K15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>2603090988</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2603090988</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>20261111</v>
-      </c>
-      <c r="B3">
-        <v>20262222</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>90</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>20271111</v>
-      </c>
-      <c r="B4">
-        <v>20272222</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
+      <c r="K16" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="G14 G16 F2:F16" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/JJsonde_reminder.xlsx
+++ b/JJsonde_reminder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BS_LeDuyBinh\automation\zaloAuto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E58E24-03EE-4D14-9136-D548C4E42254}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB331A4-25BA-4957-BD39-61142B6B2097}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="49">
   <si>
     <t>PatientID</t>
   </si>
@@ -145,16 +145,7 @@
     <t>PhoneNumber_2</t>
   </si>
   <si>
-    <t>0985930016</t>
-  </si>
-  <si>
-    <t>0965225672</t>
-  </si>
-  <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>DischargeDate</t>
@@ -182,7 +173,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -317,12 +308,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -505,7 +490,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -620,21 +605,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -680,15 +650,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1028,7 +992,7 @@
     <col min="15" max="15" width="17.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1042,7 +1006,7 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
         <v>39</v>
@@ -1054,51 +1018,52 @@
         <v>3</v>
       </c>
       <c r="I1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
         <v>7</v>
       </c>
       <c r="L1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>2511041725</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>2511041725</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="E2"/>
+      <c r="F2" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>44</v>
+      <c r="G2">
+        <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J2">
         <v>14</v>
@@ -1107,30 +1072,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2511180543</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>2511180543</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3"/>
+      <c r="F3" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>44</v>
+      <c r="G3">
+        <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J3">
         <v>90</v>
@@ -1139,30 +1105,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>2512140035</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>2512140035</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="E4"/>
+      <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>44</v>
+      <c r="G4">
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -1171,30 +1138,31 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>2512170189</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>2512170189</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="E5"/>
+      <c r="F5" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>44</v>
+      <c r="G5">
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J5">
         <v>14</v>
@@ -1203,30 +1171,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>2512251368</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>2512251368</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="E6"/>
+      <c r="F6" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>44</v>
+      <c r="G6">
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J6">
         <v>90</v>
@@ -1235,30 +1204,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>2601091619</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>2601091619</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="E7"/>
+      <c r="F7" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>41</v>
+      <c r="G7">
+        <v>985930016</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -1267,30 +1237,31 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>2601151746</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>2601151746</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="E8"/>
+      <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>44</v>
+      <c r="G8">
+        <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J8">
         <v>14</v>
@@ -1299,30 +1270,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>2601191279</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9">
         <v>2601191279</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="E9"/>
+      <c r="F9" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>44</v>
+      <c r="G9">
+        <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J9">
         <v>90</v>
@@ -1331,30 +1303,31 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>2601231940</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10">
         <v>2601231940</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="E10"/>
+      <c r="F10" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>44</v>
+      <c r="G10">
+        <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J10">
         <v>7</v>
@@ -1363,30 +1336,31 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>2602123397</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11">
         <v>2602123397</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="E11"/>
+      <c r="F11" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>44</v>
+      <c r="G11">
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J11">
         <v>14</v>
@@ -1395,30 +1369,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>2602261042</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12">
         <v>2602261042</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="E12"/>
+      <c r="F12" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>44</v>
+      <c r="G12">
+        <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J12">
         <v>90</v>
@@ -1427,30 +1402,31 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>2602260176</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13">
         <v>2602260176</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="E13"/>
+      <c r="F13" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>44</v>
+      <c r="G13">
+        <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J13">
         <v>7</v>
@@ -1459,107 +1435,83 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2603090460</v>
+      </c>
+      <c r="B14">
+        <v>2603090460</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14"/>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14">
+        <v>90</v>
+      </c>
+      <c r="K14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>2603090988</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B15">
         <v>2603090988</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D15" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="E15"/>
+      <c r="F15" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I14" t="s">
-        <v>50</v>
-      </c>
-      <c r="J14">
+      <c r="G15">
+        <v>965225672</v>
+      </c>
+      <c r="H15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15">
         <v>14</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
-        <v>2603090460</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2603090460</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" t="s">
-        <v>50</v>
-      </c>
-      <c r="J15">
-        <v>90</v>
-      </c>
-      <c r="K15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
-        <v>2603090988</v>
-      </c>
-      <c r="B16" s="2">
-        <v>2603090988</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16">
-        <v>14</v>
-      </c>
-      <c r="K16" t="s">
-        <v>8</v>
-      </c>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="G14 G16 F2:F16" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/JJsonde_reminder.xlsx
+++ b/JJsonde_reminder.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BS_LeDuyBinh\automation\zaloAuto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/binh_d_le/Working/2026_automation/zaloAuto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB331A4-25BA-4957-BD39-61142B6B2097}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75B4DE3-55B3-7342-9ABF-D4175FEE9654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="23260" windowHeight="12580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JJsonde_reminder" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="67">
   <si>
     <t>PatientID</t>
   </si>
@@ -163,17 +163,71 @@
     <t>ThirdReminderDate</t>
   </si>
   <si>
-    <t>25/03/2026</t>
-  </si>
-  <si>
     <t>Age</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>22/03/2026</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>15/03/2026</t>
+  </si>
+  <si>
+    <t>0215241</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -304,6 +358,12 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -974,543 +1034,564 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.09765625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="15.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.8984375" customWidth="1"/>
-    <col min="10" max="10" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.69921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.09765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.1640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
         <v>2511041725</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>2511041725</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2"/>
-      <c r="F2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="1">
+        <v>14</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2511180543</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2511180543</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="1">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2">
+      <c r="H3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="1">
+        <v>90</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>2512140035</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2512140035</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="1">
+        <v>7</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>2512170189</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2512170189</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="1">
         <v>14</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2511180543</v>
-      </c>
-      <c r="B3">
-        <v>2511180543</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>2512251368</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2512251368</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3"/>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3">
+      <c r="E6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3">
+      <c r="H6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="1">
         <v>90</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2512140035</v>
-      </c>
-      <c r="B4">
-        <v>2512140035</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>2601091619</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2601091619</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4"/>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4">
+      <c r="E7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="1">
+        <v>985930016</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="1">
+        <v>7</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>2601151746</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2601151746</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4">
+      <c r="H8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="1">
+        <v>14</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>2601191279</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2601191279</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="1">
+        <v>90</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>2601231940</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2601231940</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="1">
         <v>7</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2512170189</v>
-      </c>
-      <c r="B5">
-        <v>2512170189</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>2602123397</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2602123397</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="1">
+        <v>14</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>2602261042</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2602261042</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="1">
+        <v>90</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>2602260176</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2602260176</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5"/>
-      <c r="F5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5">
+      <c r="E13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5">
+      <c r="H13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="1">
+        <v>7</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>2603090460</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2603090460</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="1">
+        <v>90</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>2603090988</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2603090988</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="1">
+        <v>965225672</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="1">
         <v>14</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K15" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>2512251368</v>
-      </c>
-      <c r="B6">
-        <v>2512251368</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6"/>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6">
-        <v>90</v>
-      </c>
-      <c r="K6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>2601091619</v>
-      </c>
-      <c r="B7">
-        <v>2601091619</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7"/>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7">
-        <v>985930016</v>
-      </c>
-      <c r="H7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7">
-        <v>7</v>
-      </c>
-      <c r="K7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>2601151746</v>
-      </c>
-      <c r="B8">
-        <v>2601151746</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8"/>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>2601191279</v>
-      </c>
-      <c r="B9">
-        <v>2601191279</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9"/>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9">
-        <v>90</v>
-      </c>
-      <c r="K9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>2601231940</v>
-      </c>
-      <c r="B10">
-        <v>2601231940</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10"/>
-      <c r="F10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" t="s">
-        <v>47</v>
-      </c>
-      <c r="J10">
-        <v>7</v>
-      </c>
-      <c r="K10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>2602123397</v>
-      </c>
-      <c r="B11">
-        <v>2602123397</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11"/>
-      <c r="F11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" t="s">
-        <v>47</v>
-      </c>
-      <c r="J11">
-        <v>14</v>
-      </c>
-      <c r="K11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>2602261042</v>
-      </c>
-      <c r="B12">
-        <v>2602261042</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12"/>
-      <c r="F12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12" t="s">
-        <v>47</v>
-      </c>
-      <c r="J12">
-        <v>90</v>
-      </c>
-      <c r="K12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>2602260176</v>
-      </c>
-      <c r="B13">
-        <v>2602260176</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13"/>
-      <c r="F13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" t="s">
-        <v>47</v>
-      </c>
-      <c r="J13">
-        <v>7</v>
-      </c>
-      <c r="K13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>2603090460</v>
-      </c>
-      <c r="B14">
-        <v>2603090460</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14"/>
-      <c r="F14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" t="s">
-        <v>47</v>
-      </c>
-      <c r="I14" t="s">
-        <v>47</v>
-      </c>
-      <c r="J14">
-        <v>90</v>
-      </c>
-      <c r="K14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>2603090988</v>
-      </c>
-      <c r="B15">
-        <v>2603090988</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15"/>
-      <c r="F15" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15">
-        <v>965225672</v>
-      </c>
-      <c r="H15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15">
-        <v>14</v>
-      </c>
-      <c r="K15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
